--- a/investments/share_profit_target_calculator.xlsx
+++ b/investments/share_profit_target_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\AI\Dynamous\Courses\second-brain-workshop\investments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3184FDE7-C380-439C-80BC-CBAB5D0E556A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9B0079-0AC1-4E62-9EEB-5DC28B9A1A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -510,7 +510,7 @@
       </c>
       <c r="B12" s="7">
         <f>(B5*B6+B7+B8+B9)/B5</f>
-        <v>9.48</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
       </c>
       <c r="B13" s="4">
         <f>B12*B5</f>
-        <v>4740</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -537,7 +537,7 @@
       </c>
       <c r="B15" s="4">
         <f>B13-B14-B8</f>
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -571,7 +571,7 @@
       </c>
       <c r="B20" s="4">
         <f>B19-B9</f>
-        <v>925</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">

--- a/investments/share_profit_target_calculator.xlsx
+++ b/investments/share_profit_target_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\AI\Dynamous\Courses\second-brain-workshop\investments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9B0079-0AC1-4E62-9EEB-5DC28B9A1A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE07A50-453B-4AE3-99F2-FA2E596E5AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -461,7 +461,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -469,7 +469,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="3">
-        <v>8.48</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>900</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -510,7 +510,7 @@
       </c>
       <c r="B12" s="7">
         <f>(B5*B6+B7+B8+B9)/B5</f>
-        <v>10.28</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
       </c>
       <c r="B13" s="4">
         <f>B12*B5</f>
-        <v>5140</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -528,7 +528,7 @@
       </c>
       <c r="B14" s="4">
         <f>B5*B6+B7</f>
-        <v>4240</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -537,7 +537,7 @@
       </c>
       <c r="B15" s="4">
         <f>B13-B14-B8</f>
-        <v>900</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>11.33</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -562,7 +562,7 @@
       </c>
       <c r="B19" s="4">
         <f>B18*B5-B14-B8</f>
-        <v>1425</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -571,7 +571,7 @@
       </c>
       <c r="B20" s="4">
         <f>B19-B9</f>
-        <v>525</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
